--- a/output/ga_results/ga_report.xlsx
+++ b/output/ga_results/ga_report.xlsx
@@ -20866,7 +20866,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-01-22T15:32:20.438159</t>
+          <t>2026-01-30T11:05:51.682593</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">

--- a/output/ga_results/ga_report.xlsx
+++ b/output/ga_results/ga_report.xlsx
@@ -20866,7 +20866,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-01-30T11:05:51.682593</t>
+          <t>2026-06-25T23:45:56.421349</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
